--- a/backend/plantillas/ventas/plantilla_informe.xlsx
+++ b/backend/plantillas/ventas/plantilla_informe.xlsx
@@ -22,10 +22,10 @@
     <t>Fortalezas</t>
   </si>
   <si>
-    <t>Areas de mejora</t>
-  </si>
-  <si>
-    <t>Conclusion</t>
+    <t>Áreas de mejora</t>
+  </si>
+  <si>
+    <t>Conclusión</t>
   </si>
   <si>
     <t/>
